--- a/exports/study_2026-05-12/TMC_NBeltLineRd_SuunyvaleDonutDr_2026-05-12.xlsx
+++ b/exports/study_2026-05-12/TMC_NBeltLineRd_SuunyvaleDonutDr_2026-05-12.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13005</v>
+        <v>13782</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>90</v>
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5493</v>
+        <v>6693</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5502</v>
+        <v>6702</v>
       </c>
     </row>
     <row r="9">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6943</v>
+        <v>6596</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>463</v>
+        <v>368</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7409</v>
+        <v>6967</v>
       </c>
     </row>
     <row r="10">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>12438</v>
+        <v>13310</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>95</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>465</v>
+        <v>370</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>7</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>13005</v>
+        <v>13782</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +626,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>raw events: 13005</t>
+          <t>raw events: 13782</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>90</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5493</v>
+        <v>6693</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5502</v>
+        <v>6702</v>
       </c>
     </row>
     <row r="5">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6943</v>
+        <v>6596</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>463</v>
+        <v>368</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>7409</v>
+        <v>6967</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>285</v>
+        <v>345</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>321</v>
+        <v>367</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -915,13 +915,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>602</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>320</v>
+        <v>401</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>609</v>
+        <v>682</v>
       </c>
     </row>
     <row r="6">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319</v>
+        <v>383</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1007,13 +1007,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>658</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>560</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>276</v>
+        <v>342</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1099,19 +1099,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
@@ -1123,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>549</v>
+        <v>603</v>
       </c>
     </row>
     <row r="9">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>267</v>
+        <v>312</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -1145,19 +1145,19 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>515</v>
+        <v>543</v>
       </c>
     </row>
     <row r="10">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1191,19 +1191,19 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>9</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>546</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1237,19 +1237,19 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>378</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1283,13 +1283,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>374</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1329,13 +1329,13 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>393</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1421,13 +1421,13 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>406</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1467,19 +1467,19 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1491,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>402</v>
+        <v>428</v>
       </c>
     </row>
     <row r="17">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1513,13 +1513,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>434</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1605,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>627</v>
+        <v>660</v>
       </c>
     </row>
     <row r="20">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1651,19 +1651,19 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>612</v>
+        <v>637</v>
       </c>
     </row>
     <row r="21">
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>278</v>
+        <v>365</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1697,19 +1697,19 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>748</v>
+        <v>807</v>
       </c>
     </row>
     <row r="22">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1743,19 +1743,19 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>648</v>
+        <v>700</v>
       </c>
     </row>
     <row r="23">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1789,19 +1789,19 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>339</v>
+        <v>308</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>7</v>
@@ -1813,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>627</v>
+        <v>649</v>
       </c>
     </row>
     <row r="24">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="C24" t="n">
         <v>2</v>
@@ -1835,19 +1835,19 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>656</v>
+        <v>683</v>
       </c>
     </row>
     <row r="25">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>255</v>
+        <v>326</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1881,19 +1881,19 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>2</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>716</v>
+        <v>758</v>
       </c>
     </row>
     <row r="26">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1927,19 +1927,19 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
         <v>5</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>636</v>
+        <v>659</v>
       </c>
     </row>
     <row r="27">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>5493</v>
+        <v>6693</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>5</v>
@@ -1973,19 +1973,19 @@
         <v>4</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>6943</v>
+        <v>6596</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>463</v>
+        <v>368</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>90</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>13005</v>
+        <v>13782</v>
       </c>
     </row>
   </sheetData>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>13005</v>
+        <v>13782</v>
       </c>
     </row>
     <row r="2">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13005</v>
+        <v>13782</v>
       </c>
     </row>
   </sheetData>
